--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.54649608885558</v>
+        <v>7.888805614439032</v>
       </c>
       <c r="D2" t="n">
-        <v>12.82754881376206</v>
+        <v>2.084476682236334</v>
       </c>
       <c r="E2" t="n">
-        <v>8.46956633765592</v>
+        <v>1.376304529869087</v>
       </c>
       <c r="F2" t="n">
-        <v>11.78650031632027</v>
+        <v>1.915306301402044</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.48562876416742</v>
+        <v>10.64141467417721</v>
       </c>
       <c r="D3" t="n">
-        <v>36.40054944640259</v>
+        <v>5.915089285040422</v>
       </c>
       <c r="E3" t="n">
-        <v>8.46956633765592</v>
+        <v>1.376304529869087</v>
       </c>
       <c r="F3" t="n">
-        <v>11.78650031632027</v>
+        <v>1.915306301402044</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
